--- a/ゲーム科1年/00_前期/ゲームプログラミングⅢ/サンプル/04_オリジナルゲーム制作/スケジュール.xlsx
+++ b/ゲーム科1年/00_前期/ゲームプログラミングⅢ/サンプル/04_オリジナルゲーム制作/スケジュール.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\ArakiYusuke\Textbook\ゲーム科1年\00_前期\ゲームプログラミングⅢ\サンプル\04_オリジナルゲーム制作\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FD89B75-91A0-4AB1-84D2-DBF5826283F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8AFF99B-2AF6-4923-9FEF-4A6A0E16DBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>9月</t>
     <rPh sb="1" eb="2">
@@ -97,8 +97,91 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ステージ１－１～１－４マップ作製</t>
-    <rPh sb="14" eb="16">
+    <t>プレイヤー基礎作成</t>
+    <rPh sb="5" eb="9">
+      <t>キソサクセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>持つ作成</t>
+    <rPh sb="0" eb="1">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>投げる作成</t>
+    <rPh sb="0" eb="1">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>雑魚A作成</t>
+    <rPh sb="0" eb="2">
+      <t>ザコ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>木箱基礎作成</t>
+    <rPh sb="0" eb="2">
+      <t>キバコ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>木箱完成</t>
+    <rPh sb="0" eb="2">
+      <t>キバコ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仮ステージ作成</t>
+    <rPh sb="0" eb="1">
+      <t>カリ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>鉄箱作成</t>
+    <rPh sb="0" eb="2">
+      <t>テツバコ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>バクダン箱作成</t>
+    <rPh sb="4" eb="5">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
       <t>サクセイ</t>
     </rPh>
     <phoneticPr fontId="2"/>
@@ -207,7 +290,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -280,26 +363,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -367,9 +437,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -722,31 +789,31 @@
     </row>
     <row r="2" spans="1:143" x14ac:dyDescent="0.4">
       <c r="A2" s="2"/>
-      <c r="B2" s="24">
+      <c r="B2" s="23">
         <v>1</v>
       </c>
-      <c r="C2" s="24">
+      <c r="C2" s="23">
         <v>2</v>
       </c>
-      <c r="D2" s="24">
+      <c r="D2" s="23">
         <v>3</v>
       </c>
-      <c r="E2" s="24">
+      <c r="E2" s="23">
         <v>4</v>
       </c>
-      <c r="F2" s="24">
+      <c r="F2" s="23">
         <v>5</v>
       </c>
-      <c r="G2" s="25">
+      <c r="G2" s="24">
         <v>6</v>
       </c>
-      <c r="H2" s="25">
+      <c r="H2" s="24">
         <v>7</v>
       </c>
-      <c r="I2" s="24">
+      <c r="I2" s="23">
         <v>8</v>
       </c>
-      <c r="J2" s="24">
+      <c r="J2" s="23">
         <v>9</v>
       </c>
       <c r="K2" s="6">
@@ -1154,7 +1221,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>5</v>
@@ -1164,48 +1231,64 @@
       <c r="F3" s="12"/>
       <c r="G3" s="12"/>
       <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
+      <c r="I3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
+      <c r="P3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="S3" s="5"/>
       <c r="T3" s="5"/>
       <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5"/>
-      <c r="AA3" s="5"/>
-      <c r="AB3" s="5"/>
-      <c r="AC3" s="5"/>
-      <c r="AD3" s="5"/>
+      <c r="V3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z3" s="4"/>
+      <c r="AA3" s="4"/>
+      <c r="AB3" s="4"/>
+      <c r="AC3" s="4"/>
+      <c r="AD3" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="AE3" s="5"/>
-      <c r="AF3" s="5"/>
-      <c r="AG3" s="5"/>
-      <c r="AH3" s="5"/>
-      <c r="AI3" s="5"/>
-      <c r="AJ3" s="5"/>
+      <c r="AF3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG3" s="3"/>
+      <c r="AH3" s="3"/>
+      <c r="AI3" s="3"/>
+      <c r="AJ3" s="3"/>
       <c r="AK3" s="5"/>
       <c r="AL3" s="5"/>
-      <c r="AM3" s="5"/>
-      <c r="AN3" s="5"/>
+      <c r="AM3" s="4"/>
+      <c r="AN3" s="4"/>
       <c r="AO3" s="5"/>
       <c r="AP3" s="5"/>
       <c r="AQ3" s="5"/>
       <c r="AR3" s="5"/>
-      <c r="AS3" s="5"/>
-      <c r="AT3" s="5"/>
-      <c r="AU3" s="5"/>
-      <c r="AV3" s="5"/>
-      <c r="AW3" s="5"/>
-      <c r="AX3" s="5"/>
+      <c r="AS3" s="3"/>
+      <c r="AT3" s="3"/>
+      <c r="AU3" s="3"/>
+      <c r="AV3" s="4"/>
+      <c r="AW3" s="4"/>
+      <c r="AX3" s="4"/>
       <c r="AY3" s="5"/>
       <c r="AZ3" s="5"/>
       <c r="BA3" s="5"/>
@@ -1302,15 +1385,15 @@
     </row>
     <row r="4" spans="1:143" x14ac:dyDescent="0.4">
       <c r="A4" s="17"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
@@ -1532,6 +1615,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101005F0D9E193D28814892BA96752E68B42F" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="7ef2c4f7c5cf37d6221d7b1dda883374">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c" xmlns:ns3="26553de7-2a3a-444c-a024-df4cb947fd03" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="725cefcd41332f88909580cd13155635" ns2:_="" ns3:_="">
     <xsd:import namespace="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
@@ -1726,17 +1820,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1747,6 +1830,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4AC433-DB2B-4AE9-979C-606A42CB94A1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
+    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{974AEB67-0EB4-422A-8375-3AEC86DF31AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1765,17 +1859,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4AC433-DB2B-4AE9-979C-606A42CB94A1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
-    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDC1435B-6AB6-4AB2-8181-7AB2A8D90409}">
   <ds:schemaRefs>

--- a/ゲーム科1年/00_前期/ゲームプログラミングⅢ/サンプル/04_オリジナルゲーム制作/スケジュール.xlsx
+++ b/ゲーム科1年/00_前期/ゲームプログラミングⅢ/サンプル/04_オリジナルゲーム制作/スケジュール.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\ArakiYusuke\Textbook\ゲーム科1年\00_前期\ゲームプログラミングⅢ\サンプル\04_オリジナルゲーム制作\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8AFF99B-2AF6-4923-9FEF-4A6A0E16DBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D5FDC1F-9E0B-41A9-9050-14AFD142E5D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>9月</t>
     <rPh sb="1" eb="2">
@@ -167,23 +167,34 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>鉄箱作成</t>
-    <rPh sb="0" eb="2">
-      <t>テツバコ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
+    <t>各ハコ作成</t>
+    <rPh sb="0" eb="1">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
       <t>サクセイ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>バクダン箱作成</t>
-    <rPh sb="4" eb="5">
-      <t>バコ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
+    <t>各敵作成</t>
+    <rPh sb="0" eb="1">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="1" eb="4">
+      <t>テキサクセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ギミック＆コース作成</t>
+    <rPh sb="8" eb="10">
       <t>サクセイ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>QA</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -369,7 +380,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -409,9 +420,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -428,12 +436,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
@@ -446,6 +448,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -789,31 +797,31 @@
     </row>
     <row r="2" spans="1:143" x14ac:dyDescent="0.4">
       <c r="A2" s="2"/>
-      <c r="B2" s="23">
+      <c r="B2" s="20">
         <v>1</v>
       </c>
-      <c r="C2" s="23">
+      <c r="C2" s="20">
         <v>2</v>
       </c>
-      <c r="D2" s="23">
+      <c r="D2" s="20">
         <v>3</v>
       </c>
-      <c r="E2" s="23">
+      <c r="E2" s="20">
         <v>4</v>
       </c>
-      <c r="F2" s="23">
+      <c r="F2" s="20">
         <v>5</v>
       </c>
-      <c r="G2" s="24">
+      <c r="G2" s="21">
         <v>6</v>
       </c>
-      <c r="H2" s="24">
+      <c r="H2" s="21">
         <v>7</v>
       </c>
-      <c r="I2" s="23">
+      <c r="I2" s="20">
         <v>8</v>
       </c>
-      <c r="J2" s="23">
+      <c r="J2" s="20">
         <v>9</v>
       </c>
       <c r="K2" s="6">
@@ -1217,7 +1225,7 @@
       </c>
     </row>
     <row r="3" spans="1:143" x14ac:dyDescent="0.4">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="19" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="12" t="s">
@@ -1268,114 +1276,118 @@
         <v>18</v>
       </c>
       <c r="AE3" s="5"/>
-      <c r="AF3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG3" s="3"/>
-      <c r="AH3" s="3"/>
-      <c r="AI3" s="3"/>
-      <c r="AJ3" s="3"/>
+      <c r="AF3" s="5"/>
+      <c r="AG3" s="5"/>
+      <c r="AH3" s="5"/>
+      <c r="AI3" s="5"/>
+      <c r="AJ3" s="5"/>
       <c r="AK3" s="5"/>
       <c r="AL3" s="5"/>
-      <c r="AM3" s="4"/>
-      <c r="AN3" s="4"/>
+      <c r="AM3" s="5"/>
+      <c r="AN3" s="5"/>
       <c r="AO3" s="5"/>
       <c r="AP3" s="5"/>
       <c r="AQ3" s="5"/>
       <c r="AR3" s="5"/>
-      <c r="AS3" s="3"/>
-      <c r="AT3" s="3"/>
-      <c r="AU3" s="3"/>
-      <c r="AV3" s="4"/>
-      <c r="AW3" s="4"/>
-      <c r="AX3" s="4"/>
+      <c r="AS3" s="5"/>
+      <c r="AT3" s="5"/>
+      <c r="AU3" s="5"/>
+      <c r="AV3" s="5"/>
+      <c r="AW3" s="5"/>
+      <c r="AX3" s="5"/>
       <c r="AY3" s="5"/>
       <c r="AZ3" s="5"/>
       <c r="BA3" s="5"/>
-      <c r="BB3" s="3"/>
-      <c r="BC3" s="3"/>
-      <c r="BD3" s="3"/>
-      <c r="BE3" s="3"/>
-      <c r="BF3" s="3"/>
-      <c r="BG3" s="3"/>
-      <c r="BH3" s="3"/>
-      <c r="BI3" s="3"/>
-      <c r="BJ3" s="3"/>
-      <c r="BK3" s="4"/>
-      <c r="BL3" s="4"/>
-      <c r="BM3" s="4"/>
-      <c r="BN3" s="4"/>
-      <c r="BO3" s="4"/>
-      <c r="BP3" s="4"/>
-      <c r="BQ3" s="4"/>
-      <c r="BR3" s="21"/>
-      <c r="BS3" s="4"/>
-      <c r="BT3" s="4"/>
-      <c r="BU3" s="5"/>
-      <c r="BV3" s="5"/>
-      <c r="BW3" s="5"/>
-      <c r="BX3" s="5"/>
-      <c r="BY3" s="20"/>
-      <c r="BZ3" s="5"/>
-      <c r="CA3" s="5"/>
-      <c r="CB3" s="5"/>
-      <c r="CC3" s="20"/>
-      <c r="CD3" s="5"/>
-      <c r="CE3" s="5"/>
-      <c r="CF3" s="5"/>
-      <c r="CG3" s="5"/>
-      <c r="CH3" s="5"/>
-      <c r="CI3" s="5"/>
-      <c r="CJ3" s="5"/>
+      <c r="BB3" s="5"/>
+      <c r="BC3" s="5"/>
+      <c r="BD3" s="5"/>
+      <c r="BE3" s="5"/>
+      <c r="BF3" s="5"/>
+      <c r="BG3" s="5"/>
+      <c r="BH3" s="5"/>
+      <c r="BI3" s="5"/>
+      <c r="BJ3" s="5"/>
+      <c r="BK3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="BL3" s="3"/>
+      <c r="BM3" s="3"/>
+      <c r="BN3" s="3"/>
+      <c r="BO3" s="3"/>
+      <c r="BP3" s="3"/>
+      <c r="BQ3" s="3"/>
+      <c r="BR3" s="23"/>
+      <c r="BS3" s="3"/>
+      <c r="BT3" s="3"/>
+      <c r="BU3" s="3"/>
+      <c r="BV3" s="3"/>
+      <c r="BW3" s="3"/>
+      <c r="BX3" s="3"/>
+      <c r="BY3" s="23"/>
+      <c r="BZ3" s="3"/>
+      <c r="CA3" s="3"/>
+      <c r="CB3" s="3"/>
+      <c r="CC3" s="23"/>
+      <c r="CD3" s="3"/>
+      <c r="CE3" s="3"/>
+      <c r="CF3" s="3"/>
+      <c r="CG3" s="3"/>
+      <c r="CH3" s="3"/>
+      <c r="CI3" s="3"/>
+      <c r="CJ3" s="3"/>
       <c r="CK3" s="3"/>
       <c r="CL3" s="3"/>
       <c r="CM3" s="3"/>
       <c r="CN3" s="3"/>
-      <c r="CO3" s="3"/>
-      <c r="CP3" s="3"/>
-      <c r="CQ3" s="3"/>
-      <c r="CR3" s="3"/>
-      <c r="CS3" s="3"/>
-      <c r="CT3" s="3"/>
-      <c r="CU3" s="3"/>
-      <c r="CV3" s="3"/>
-      <c r="CW3" s="3"/>
-      <c r="CX3" s="3"/>
-      <c r="CY3" s="3"/>
-      <c r="CZ3" s="3"/>
-      <c r="DA3" s="3"/>
-      <c r="DB3" s="3"/>
-      <c r="DC3" s="3"/>
-      <c r="DD3" s="3"/>
-      <c r="DE3" s="3"/>
-      <c r="DF3" s="3"/>
-      <c r="DG3" s="3"/>
-      <c r="DH3" s="3"/>
-      <c r="DI3" s="3"/>
-      <c r="DJ3" s="3"/>
-      <c r="DK3" s="3"/>
-      <c r="DL3" s="3"/>
-      <c r="DM3" s="3"/>
-      <c r="DN3" s="3"/>
-      <c r="DO3" s="3"/>
-      <c r="DP3" s="3"/>
-      <c r="DQ3" s="3"/>
-      <c r="DR3" s="13"/>
-      <c r="DS3" s="3"/>
-      <c r="DT3" s="3"/>
-      <c r="DU3" s="3"/>
-      <c r="DV3" s="3"/>
-      <c r="DW3" s="3"/>
-      <c r="DX3" s="3"/>
-      <c r="DY3" s="3"/>
-      <c r="DZ3" s="3"/>
-      <c r="EA3" s="3"/>
-      <c r="EB3" s="3"/>
-      <c r="EC3" s="3"/>
-      <c r="ED3" s="3"/>
-      <c r="EE3" s="3"/>
-      <c r="EF3" s="3"/>
-      <c r="EG3" s="3"/>
+      <c r="CO3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="CP3" s="4"/>
+      <c r="CQ3" s="4"/>
+      <c r="CR3" s="4"/>
+      <c r="CS3" s="4"/>
+      <c r="CT3" s="4"/>
+      <c r="CU3" s="4"/>
+      <c r="CV3" s="4"/>
+      <c r="CW3" s="4"/>
+      <c r="CX3" s="4"/>
+      <c r="CY3" s="4"/>
+      <c r="CZ3" s="4"/>
+      <c r="DA3" s="4"/>
+      <c r="DB3" s="4"/>
+      <c r="DC3" s="4"/>
+      <c r="DD3" s="4"/>
+      <c r="DE3" s="4"/>
+      <c r="DF3" s="4"/>
+      <c r="DG3" s="4"/>
+      <c r="DH3" s="4"/>
+      <c r="DI3" s="4"/>
+      <c r="DJ3" s="4"/>
+      <c r="DK3" s="4"/>
+      <c r="DL3" s="4"/>
+      <c r="DM3" s="4"/>
+      <c r="DN3" s="4"/>
+      <c r="DO3" s="4"/>
+      <c r="DP3" s="4"/>
+      <c r="DQ3" s="4"/>
+      <c r="DR3" s="24"/>
+      <c r="DS3" s="4"/>
+      <c r="DT3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="DU3" s="5"/>
+      <c r="DV3" s="5"/>
+      <c r="DW3" s="5"/>
+      <c r="DX3" s="5"/>
+      <c r="DY3" s="5"/>
+      <c r="DZ3" s="5"/>
+      <c r="EA3" s="5"/>
+      <c r="EB3" s="5"/>
+      <c r="EC3" s="5"/>
+      <c r="ED3" s="5"/>
+      <c r="EE3" s="5"/>
+      <c r="EF3" s="5"/>
+      <c r="EG3" s="5"/>
       <c r="EH3" s="2"/>
       <c r="EI3" s="2"/>
       <c r="EJ3" s="2"/>
@@ -1384,147 +1396,147 @@
       <c r="EM3" s="2"/>
     </row>
     <row r="4" spans="1:143" x14ac:dyDescent="0.4">
-      <c r="A4" s="17"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
-      <c r="O4" s="18"/>
-      <c r="P4" s="18"/>
-      <c r="Q4" s="18"/>
-      <c r="R4" s="18"/>
-      <c r="S4" s="18"/>
-      <c r="T4" s="18"/>
-      <c r="U4" s="18"/>
-      <c r="V4" s="18"/>
-      <c r="W4" s="18"/>
-      <c r="X4" s="18"/>
-      <c r="Y4" s="18"/>
-      <c r="Z4" s="18"/>
-      <c r="AA4" s="18"/>
-      <c r="AB4" s="18"/>
-      <c r="AC4" s="18"/>
-      <c r="AD4" s="18"/>
-      <c r="AE4" s="18"/>
-      <c r="AF4" s="18"/>
-      <c r="AG4" s="18"/>
-      <c r="AH4" s="18"/>
-      <c r="AI4" s="18"/>
-      <c r="AJ4" s="18"/>
-      <c r="AK4" s="18"/>
-      <c r="AL4" s="18"/>
-      <c r="AM4" s="18"/>
-      <c r="AN4" s="18"/>
-      <c r="AO4" s="18"/>
-      <c r="AP4" s="18"/>
-      <c r="AQ4" s="18"/>
-      <c r="AR4" s="18"/>
-      <c r="AS4" s="18"/>
-      <c r="AT4" s="18"/>
-      <c r="AU4" s="18"/>
-      <c r="AV4" s="18"/>
-      <c r="AW4" s="18"/>
-      <c r="AX4" s="18"/>
-      <c r="AY4" s="18"/>
-      <c r="AZ4" s="18"/>
-      <c r="BA4" s="18"/>
-      <c r="BB4" s="18"/>
-      <c r="BC4" s="18"/>
-      <c r="BD4" s="18"/>
-      <c r="BE4" s="18"/>
-      <c r="BF4" s="18"/>
-      <c r="BG4" s="17"/>
-      <c r="BH4" s="17"/>
-      <c r="BI4" s="17"/>
-      <c r="BJ4" s="17"/>
-      <c r="BK4" s="17"/>
-      <c r="BL4" s="17"/>
-      <c r="BM4" s="17"/>
-      <c r="BN4" s="17"/>
-      <c r="BO4" s="15" t="s">
+      <c r="A4" s="16"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="17"/>
+      <c r="U4" s="17"/>
+      <c r="V4" s="17"/>
+      <c r="W4" s="17"/>
+      <c r="X4" s="17"/>
+      <c r="Y4" s="17"/>
+      <c r="Z4" s="17"/>
+      <c r="AA4" s="17"/>
+      <c r="AB4" s="17"/>
+      <c r="AC4" s="17"/>
+      <c r="AD4" s="17"/>
+      <c r="AE4" s="17"/>
+      <c r="AF4" s="17"/>
+      <c r="AG4" s="17"/>
+      <c r="AH4" s="17"/>
+      <c r="AI4" s="17"/>
+      <c r="AJ4" s="17"/>
+      <c r="AK4" s="17"/>
+      <c r="AL4" s="17"/>
+      <c r="AM4" s="17"/>
+      <c r="AN4" s="17"/>
+      <c r="AO4" s="17"/>
+      <c r="AP4" s="17"/>
+      <c r="AQ4" s="17"/>
+      <c r="AR4" s="17"/>
+      <c r="AS4" s="17"/>
+      <c r="AT4" s="17"/>
+      <c r="AU4" s="17"/>
+      <c r="AV4" s="17"/>
+      <c r="AW4" s="17"/>
+      <c r="AX4" s="17"/>
+      <c r="AY4" s="17"/>
+      <c r="AZ4" s="17"/>
+      <c r="BA4" s="17"/>
+      <c r="BB4" s="17"/>
+      <c r="BC4" s="17"/>
+      <c r="BD4" s="17"/>
+      <c r="BE4" s="17"/>
+      <c r="BF4" s="17"/>
+      <c r="BG4" s="16"/>
+      <c r="BH4" s="16"/>
+      <c r="BI4" s="16"/>
+      <c r="BJ4" s="16"/>
+      <c r="BK4" s="16"/>
+      <c r="BL4" s="16"/>
+      <c r="BM4" s="16"/>
+      <c r="BN4" s="16"/>
+      <c r="BO4" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="BP4" s="17"/>
-      <c r="BQ4" s="17"/>
-      <c r="BR4" s="17"/>
-      <c r="BS4" s="17"/>
-      <c r="BT4" s="17"/>
-      <c r="BU4" s="17"/>
-      <c r="BV4" s="17"/>
-      <c r="BW4" s="17"/>
-      <c r="BX4" s="17"/>
-      <c r="BY4" s="17"/>
-      <c r="BZ4" s="17"/>
-      <c r="CA4" s="17"/>
-      <c r="CB4" s="17"/>
-      <c r="CC4" s="17"/>
-      <c r="CD4" s="17"/>
-      <c r="CE4" s="17"/>
-      <c r="CF4" s="17"/>
-      <c r="CG4" s="17"/>
-      <c r="CH4" s="17"/>
-      <c r="CI4" s="17"/>
-      <c r="CJ4" s="17"/>
-      <c r="CK4" s="17"/>
-      <c r="CL4" s="14" t="s">
+      <c r="BP4" s="16"/>
+      <c r="BQ4" s="16"/>
+      <c r="BR4" s="16"/>
+      <c r="BS4" s="16"/>
+      <c r="BT4" s="16"/>
+      <c r="BU4" s="16"/>
+      <c r="BV4" s="16"/>
+      <c r="BW4" s="16"/>
+      <c r="BX4" s="16"/>
+      <c r="BY4" s="16"/>
+      <c r="BZ4" s="16"/>
+      <c r="CA4" s="16"/>
+      <c r="CB4" s="16"/>
+      <c r="CC4" s="16"/>
+      <c r="CD4" s="16"/>
+      <c r="CE4" s="16"/>
+      <c r="CF4" s="16"/>
+      <c r="CG4" s="16"/>
+      <c r="CH4" s="16"/>
+      <c r="CI4" s="16"/>
+      <c r="CJ4" s="16"/>
+      <c r="CK4" s="16"/>
+      <c r="CL4" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CM4" s="17"/>
-      <c r="CN4" s="17"/>
-      <c r="CO4" s="17"/>
-      <c r="CP4" s="17"/>
-      <c r="CQ4" s="17"/>
-      <c r="CR4" s="17"/>
-      <c r="CS4" s="17"/>
-      <c r="CT4" s="17"/>
-      <c r="CU4" s="17"/>
-      <c r="CV4" s="17"/>
-      <c r="CW4" s="17"/>
-      <c r="CX4" s="17"/>
-      <c r="CY4" s="17"/>
-      <c r="CZ4" s="17"/>
-      <c r="DA4" s="17"/>
-      <c r="DB4" s="17"/>
-      <c r="DC4" s="17"/>
-      <c r="DD4" s="17"/>
-      <c r="DE4" s="17"/>
-      <c r="DF4" s="17"/>
-      <c r="DG4" s="17"/>
-      <c r="DH4" s="17"/>
-      <c r="DI4" s="17"/>
-      <c r="DJ4" s="17"/>
-      <c r="DK4" s="17"/>
-      <c r="DL4" s="17"/>
-      <c r="DM4" s="17"/>
-      <c r="DN4" s="17"/>
-      <c r="DO4" s="17"/>
-      <c r="DP4" s="17"/>
-      <c r="DQ4" s="17"/>
-      <c r="DR4" s="17"/>
-      <c r="DS4" s="17"/>
-      <c r="DT4" s="17"/>
-      <c r="DU4" s="17"/>
-      <c r="DV4" s="17"/>
-      <c r="DW4" s="17"/>
-      <c r="DX4" s="17"/>
-      <c r="DY4" s="17"/>
-      <c r="DZ4" s="17"/>
-      <c r="EA4" s="17"/>
-      <c r="EB4" s="17"/>
-      <c r="EC4" s="17"/>
-      <c r="ED4" s="17"/>
-      <c r="EE4" s="17"/>
-      <c r="EF4" s="17"/>
-      <c r="EG4" s="17"/>
+      <c r="CM4" s="16"/>
+      <c r="CN4" s="16"/>
+      <c r="CO4" s="16"/>
+      <c r="CP4" s="16"/>
+      <c r="CQ4" s="16"/>
+      <c r="CR4" s="16"/>
+      <c r="CS4" s="16"/>
+      <c r="CT4" s="16"/>
+      <c r="CU4" s="16"/>
+      <c r="CV4" s="16"/>
+      <c r="CW4" s="16"/>
+      <c r="CX4" s="16"/>
+      <c r="CY4" s="16"/>
+      <c r="CZ4" s="16"/>
+      <c r="DA4" s="16"/>
+      <c r="DB4" s="16"/>
+      <c r="DC4" s="16"/>
+      <c r="DD4" s="16"/>
+      <c r="DE4" s="16"/>
+      <c r="DF4" s="16"/>
+      <c r="DG4" s="16"/>
+      <c r="DH4" s="16"/>
+      <c r="DI4" s="16"/>
+      <c r="DJ4" s="16"/>
+      <c r="DK4" s="16"/>
+      <c r="DL4" s="16"/>
+      <c r="DM4" s="16"/>
+      <c r="DN4" s="16"/>
+      <c r="DO4" s="16"/>
+      <c r="DP4" s="16"/>
+      <c r="DQ4" s="16"/>
+      <c r="DR4" s="16"/>
+      <c r="DS4" s="16"/>
+      <c r="DT4" s="16"/>
+      <c r="DU4" s="16"/>
+      <c r="DV4" s="16"/>
+      <c r="DW4" s="16"/>
+      <c r="DX4" s="16"/>
+      <c r="DY4" s="16"/>
+      <c r="DZ4" s="16"/>
+      <c r="EA4" s="16"/>
+      <c r="EB4" s="16"/>
+      <c r="EC4" s="16"/>
+      <c r="ED4" s="16"/>
+      <c r="EE4" s="16"/>
+      <c r="EF4" s="16"/>
+      <c r="EG4" s="16"/>
       <c r="EH4" s="10" t="s">
         <v>8</v>
       </c>
@@ -1537,71 +1549,71 @@
       </c>
     </row>
     <row r="5" spans="1:143" x14ac:dyDescent="0.4">
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="16"/>
-      <c r="S5" s="16"/>
-      <c r="T5" s="16"/>
-      <c r="U5" s="16"/>
-      <c r="V5" s="16"/>
-      <c r="W5" s="16"/>
-      <c r="X5" s="16"/>
-      <c r="Y5" s="16"/>
-      <c r="Z5" s="16"/>
-      <c r="AA5" s="16"/>
-      <c r="AB5" s="16"/>
-      <c r="AC5" s="16"/>
-      <c r="AD5" s="16"/>
-      <c r="AE5" s="16"/>
-      <c r="AF5" s="16"/>
-      <c r="AG5" s="16"/>
-      <c r="AH5" s="16"/>
-      <c r="AI5" s="16"/>
-      <c r="AJ5" s="16"/>
-      <c r="AK5" s="16"/>
-      <c r="AL5" s="16"/>
-      <c r="AM5" s="16"/>
-      <c r="AN5" s="16"/>
-      <c r="AO5" s="16"/>
-      <c r="AP5" s="16"/>
-      <c r="AQ5" s="16"/>
-      <c r="AR5" s="16"/>
-      <c r="AS5" s="16"/>
-      <c r="AT5" s="16"/>
-      <c r="AU5" s="16"/>
-      <c r="AV5" s="16"/>
-      <c r="AW5" s="16"/>
-      <c r="AX5" s="16"/>
-      <c r="AY5" s="16"/>
-      <c r="AZ5" s="16"/>
-      <c r="BA5" s="16"/>
-      <c r="BB5" s="16"/>
-      <c r="BC5" s="16"/>
-      <c r="BD5" s="16"/>
-      <c r="BE5" s="16"/>
-      <c r="BF5" s="16"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
+      <c r="S5" s="15"/>
+      <c r="T5" s="15"/>
+      <c r="U5" s="15"/>
+      <c r="V5" s="15"/>
+      <c r="W5" s="15"/>
+      <c r="X5" s="15"/>
+      <c r="Y5" s="15"/>
+      <c r="Z5" s="15"/>
+      <c r="AA5" s="15"/>
+      <c r="AB5" s="15"/>
+      <c r="AC5" s="15"/>
+      <c r="AD5" s="15"/>
+      <c r="AE5" s="15"/>
+      <c r="AF5" s="15"/>
+      <c r="AG5" s="15"/>
+      <c r="AH5" s="15"/>
+      <c r="AI5" s="15"/>
+      <c r="AJ5" s="15"/>
+      <c r="AK5" s="15"/>
+      <c r="AL5" s="15"/>
+      <c r="AM5" s="15"/>
+      <c r="AN5" s="15"/>
+      <c r="AO5" s="15"/>
+      <c r="AP5" s="15"/>
+      <c r="AQ5" s="15"/>
+      <c r="AR5" s="15"/>
+      <c r="AS5" s="15"/>
+      <c r="AT5" s="15"/>
+      <c r="AU5" s="15"/>
+      <c r="AV5" s="15"/>
+      <c r="AW5" s="15"/>
+      <c r="AX5" s="15"/>
+      <c r="AY5" s="15"/>
+      <c r="AZ5" s="15"/>
+      <c r="BA5" s="15"/>
+      <c r="BB5" s="15"/>
+      <c r="BC5" s="15"/>
+      <c r="BD5" s="15"/>
+      <c r="BE5" s="15"/>
+      <c r="BF5" s="15"/>
     </row>
     <row r="13" spans="1:143" x14ac:dyDescent="0.4">
-      <c r="EH13" s="19"/>
-      <c r="EI13" s="19"/>
-      <c r="EJ13" s="19"/>
-      <c r="EK13" s="19"/>
-      <c r="EL13" s="19"/>
-      <c r="EM13" s="19"/>
+      <c r="EH13" s="18"/>
+      <c r="EI13" s="18"/>
+      <c r="EJ13" s="18"/>
+      <c r="EK13" s="18"/>
+      <c r="EL13" s="18"/>
+      <c r="EM13" s="18"/>
     </row>
     <row r="14" spans="1:143" x14ac:dyDescent="0.4">
       <c r="BO14" s="1"/>
@@ -1615,17 +1627,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101005F0D9E193D28814892BA96752E68B42F" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="7ef2c4f7c5cf37d6221d7b1dda883374">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c" xmlns:ns3="26553de7-2a3a-444c-a024-df4cb947fd03" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="725cefcd41332f88909580cd13155635" ns2:_="" ns3:_="">
     <xsd:import namespace="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
@@ -1820,6 +1821,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1830,17 +1842,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4AC433-DB2B-4AE9-979C-606A42CB94A1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
-    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{974AEB67-0EB4-422A-8375-3AEC86DF31AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1859,6 +1860,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4AC433-DB2B-4AE9-979C-606A42CB94A1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
+    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDC1435B-6AB6-4AB2-8181-7AB2A8D90409}">
   <ds:schemaRefs>
